--- a/data/waste_train.xlsx
+++ b/data/waste_train.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="48">
   <si>
     <t>종이류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,6 +199,22 @@
   </si>
   <si>
     <t>data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마우스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플라스틱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플라스틱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -529,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.875" bestFit="1" customWidth="1"/>
@@ -816,6 +832,22 @@
         <v>39</v>
       </c>
     </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
